--- a/forms/trg/Formulir_TRG_addis.xlsx
+++ b/forms/trg/Formulir_TRG_addis.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B38)</f>
+        <f>COUNTA(Anggota!B5:B39)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F38)</f>
+        <f>COUNTA(Anggota!F5:F39)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. drh. Fika Yuliza Purba, M.Sc.</t>
+          <t>Prof. Dr. drh. Dwi Kesuma Sari, APVet.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Reproduction</t>
+          <t>Veterinary Pathology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +937,13 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9483-3876</t>
+          <t>0000-0002-5326-3336</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57207245968</t>
+          <t>6601992438</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>drh. Andi Magfira Satya Apada, M.Sc.</t>
+          <t>Dr. drh. Fika Yuliza Purba, M.Sc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,18 +973,22 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Microbiology</t>
+          <t>Veterinary Reproduction</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9483-3876</t>
+        </is>
+      </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212135496</t>
+          <t>https://www.scopus.com/pages/authors/57207245968</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -999,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Abdul Wahid Jamaluddin, S.Farm., M.Farm., Apt.</t>
+          <t>drh. Andi Magfira Satya Apada, M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,22 +1018,18 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Pharmacology</t>
+          <t>Veterinary Microbiology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2143-9069</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212139565</t>
+          <t>https://www.scopus.com/pages/authors/57212135496</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>drh. Nurul Sulfi Andini, M.Sc.</t>
+          <t>Abdul Wahid Jamaluddin, S.Farm., M.Farm., Apt.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Pathology</t>
+          <t>Veterinary Pharmacology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1068,13 +1068,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6354-0782</t>
+          <t>0000-0002-2143-9069</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212145929</t>
+          <t>https://www.scopus.com/pages/authors/57212139565</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>drh. Rini Amriani, M.Biomed.</t>
+          <t>drh. Nurul Sulfi Andini, M.Sc.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Biochemistry</t>
+          <t>Veterinary Pathology</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1113,13 +1113,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6212-9000</t>
+          <t>0000-0001-6354-0782</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57314114000</t>
+          <t>https://www.scopus.com/pages/authors/57212145929</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Irma Andriani, M.Si.</t>
+          <t>drh. Rini Amriani, M.Biomed.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Veterinary Biochemistry</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1158,13 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1268-6559</t>
+          <t>0000-0001-6212-9000</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57201349838</t>
+          <t>https://www.scopus.com/pages/authors/57314114000</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mohd Farhan Hanif Reduan</t>
+          <t>Dr. Irma Andriani, M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Kelantan Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Clinical Pathology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1203,13 +1203,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0815-8761</t>
+          <t>0000-0003-1268-6559</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212141002</t>
+          <t>https://www.scopus.com/pages/authors/57201349838</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1224,22 +1224,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>drh. Mawar Subangkit, M.Si., Ph.D.</t>
+          <t>Dr. Mohd Farhan Hanif Reduan</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>IPB University</t>
+          <t>Universiti Kelantan Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Pathology</t>
+          <t>Veterinary Clinical Pathology</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1248,13 +1248,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9098-0094</t>
+          <t>0000-0003-0815-8761</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/55413241800</t>
+          <t>https://www.scopus.com/pages/authors/57212141002</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1269,22 +1269,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>April Hari Wardhana, M.Si., Ph.D.</t>
+          <t>drh. Mawar Subangkit, M.Si., Ph.D.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>National Research and Innovation Agency</t>
+          <t>IPB University</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Parasitology</t>
+          <t>Veterinary Pathology</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1293,13 +1293,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0750-8467</t>
+          <t>0000-0002-9098-0094</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/16243031900</t>
+          <t>https://www.scopus.com/pages/authors/55413241800</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Prof. Alan P. Dargantes, DVM., MTVSc., Ph.D</t>
+          <t>April Hari Wardhana, M.Si., Ph.D.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Central Mindanao University</t>
+          <t>National Research and Innovation Agency</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1338,13 +1338,13 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-5840-4771</t>
+          <t>0000-0003-0750-8467</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/6506730472</t>
+          <t>https://www.scopus.com/pages/authors/16243031900</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Prof. Makoto Matsubayashi, DVM, Ph.D.</t>
+          <t>Prof. Alan P. Dargantes, DVM., MTVSc., Ph.D</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Osaka Metropolitan University</t>
+          <t>Central Mindanao University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1383,13 +1383,13 @@
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-2191-8919</t>
+          <t>0009-0006-5840-4771</t>
         </is>
       </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/7007040306</t>
+          <t>https://www.scopus.com/pages/authors/6506730472</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>drh. Anjani Marisa Kartikasari, M.Si.</t>
+          <t>Prof. Makoto Matsubayashi, DVM, Ph.D.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Osaka Metropolitan University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1428,13 +1428,13 @@
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8030-9010</t>
+          <t>0009-0000-2191-8919</t>
         </is>
       </c>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212500735</t>
+          <t>https://www.scopus.com/pages/authors/7007040306</t>
         </is>
       </c>
       <c r="M16" s="11" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>drh. Nur Alif Bahmid, M.Si.</t>
+          <t>drh. Anjani Marisa Kartikasari, M.Si.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Reproduction</t>
+          <t>Veterinary Parasitology</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1473,13 +1473,13 @@
       <c r="I17" s="12" t="n"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-0760-146X</t>
+          <t>0000-0002-8030-9010</t>
         </is>
       </c>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57212139201</t>
+          <t>https://www.scopus.com/pages/authors/57212500735</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>drh. Rian Hari Suharto, M.Sc.</t>
+          <t>drh. Nur Alif Bahmid, M.Si.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Epidemiology</t>
+          <t>Veterinary Reproduction</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1518,13 +1518,13 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-0753-535X</t>
+          <t>0009-0009-0760-146X</t>
         </is>
       </c>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/60001699800</t>
+          <t>https://www.scopus.com/pages/authors/57212139201</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>drh. Anak Agung P.J. Wahyuda, M.Si.</t>
+          <t>drh. Rian Hari Suharto, M.Sc.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Public Health</t>
+          <t>Veterinary Epidemiology</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1563,13 +1563,13 @@
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-2673-5107</t>
+          <t>0009-0006-0753-535X</t>
         </is>
       </c>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/60174868500</t>
+          <t>https://www.scopus.com/pages/authors/60001699800</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>drh. Muh. Zulfadillah Sinusi, M.Sc.</t>
+          <t>drh. Anak Agung P.J. Wahyuda, M.Si.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Surgery and Radiology</t>
+          <t>Veterinary Public Health</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1608,13 +1608,13 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7738-0879</t>
+          <t>0009-0001-2673-5107</t>
         </is>
       </c>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57329103000</t>
+          <t>https://www.scopus.com/pages/authors/60174868500</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>drh. Dian Fatmawati, M.Biomed.</t>
+          <t>drh. Muh. Zulfadillah Sinusi, M.Sc.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Internal Medicine</t>
+          <t>Veterinary Surgery and Radiology</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1653,13 +1653,13 @@
       <c r="I21" s="12" t="n"/>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-6815-8553</t>
+          <t>0000-0002-7738-0879</t>
         </is>
       </c>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/60609036400</t>
+          <t>https://www.scopus.com/pages/authors/57329103000</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>drh. Zulfikri Mustakdir, M.Si.</t>
+          <t>drh. Dian Fatmawati, M.Biomed.</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Parasitology</t>
+          <t>Veterinary Internal Medicine</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1698,13 +1698,13 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>0009-0004-9278-6967</t>
+          <t>0009-0009-6815-8553</t>
         </is>
       </c>
       <c r="K22" s="12" t="n"/>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/60577504700</t>
+          <t>https://www.scopus.com/pages/authors/60609036400</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>drh. Muh. Dirga Gifardi, M.Si.</t>
+          <t>drh. Zulfikri Mustakdir, M.Si.</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Anatomy</t>
+          <t>Veterinary Parasitology</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1743,13 +1743,13 @@
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-4158-7620</t>
+          <t>0009-0004-9278-6967</t>
         </is>
       </c>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>https://www.scopus.com/pages/authors/57857891000</t>
+          <t>https://www.scopus.com/pages/authors/60577504700</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>drh. Danawir Alwi</t>
+          <t>drh. Muh. Dirga Gifardi, M.Si.</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Microbiology</t>
+          <t>Veterinary Anatomy</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1788,11 +1788,15 @@
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>0009-0002-4560-9138</t>
+          <t>0009-0006-4158-7620</t>
         </is>
       </c>
       <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/57857891000</t>
+        </is>
+      </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1805,12 +1809,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>drh. A. Rifqatul Ummah, M.Sc.</t>
+          <t>drh. Danawir Alwi</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1820,7 +1824,7 @@
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Surgery and Radiology</t>
+          <t>Veterinary Microbiology</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1829,15 +1833,11 @@
       <c r="I25" s="12" t="n"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-6683-4087</t>
+          <t>0009-0002-4560-9138</t>
         </is>
       </c>
       <c r="K25" s="12" t="n"/>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>https://www.scopus.com/pages/authors/60608907100</t>
-        </is>
-      </c>
+      <c r="L25" s="12" t="n"/>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>drh. Sitti Mughniati, M.Biomed.</t>
+          <t>drh. A. Rifqatul Ummah, M.Sc.</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Veterinary Anatomy</t>
+          <t>Veterinary Surgery and Radiology</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1874,11 +1874,15 @@
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-5570-7679</t>
+          <t>0009-0009-6683-4087</t>
         </is>
       </c>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scopus.com/pages/authors/60608907100</t>
+        </is>
+      </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1889,18 +1893,42 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>drh. Sitti Mughniati, M.Biomed.</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Veterinary Anatomy</t>
+        </is>
+      </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>0009-0003-5570-7679</t>
+        </is>
+      </c>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2089,15 +2117,32 @@
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
